--- a/3.5/html/_downloads/ff9554ff9ff6240811c20ede15113dbd/ModelZoo_Github.xlsx
+++ b/3.5/html/_downloads/ff9554ff9ff6240811c20ede15113dbd/ModelZoo_Github.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temp\vitis-ai-staging\docsrc\source\docs\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B78BE58-FC16-4D36-83B5-528EE33229ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28D1299B-06B6-4ECA-9ED5-CA546B84F694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{FDEDB1A0-B1D7-4FF6-B821-F3B34B308466}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="384">
   <si>
     <t>Task</t>
   </si>
@@ -819,6 +819,17 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>E2E throughput (fps) 
+Single Thread</t>
+  </si>
+  <si>
+    <t>E2E throughput (fps) 
+Multi Thread</t>
+  </si>
+  <si>
+    <t>4PE DPUCVDX8H @350MHz Gen4x8</t>
+  </si>
+  <si>
     <t>Non-Commercial Use Only</t>
   </si>
   <si>
@@ -1289,6 +1300,15 @@
   </si>
   <si>
     <t>Copyleft Model Zoo</t>
+  </si>
+  <si>
+    <t>V70</t>
+  </si>
+  <si>
+    <t>VEK280</t>
+  </si>
+  <si>
+    <t>1* C20B14CU1 @ 300MHz</t>
   </si>
   <si>
     <t>/</t>
@@ -1338,27 +1358,6 @@
       </rPr>
       <t>Copyright 2023 Advanced Micro Devices, Inc.</t>
     </r>
-  </si>
-  <si>
-    <t>V70
-E2E throughput (fps) 
-Multi Thread
-1* C20B14CU1 @250MHz Gen4x8
-AIE-ML fclk=1.00GHz</t>
-  </si>
-  <si>
-    <t>VEK280
-E2E throughput (fps) 
-Multi Thread
-1* C20B14CU1 @300MHz
-AIE-ML fclk=1.18GHz</t>
-  </si>
-  <si>
-    <t>VEK280
-E2E throughput (fps) 
-Single Thread
-1* C20B14CU1 @ 300MHz
-AIE-ML fclk=1.18GHz</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1421,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1434,6 +1433,32 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1459,7 +1484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1539,26 +1564,29 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1899,34 +1927,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="31"/>
+      <c r="R1" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="S1" s="32"/>
+      <c r="T1" s="34" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="2" spans="1:20" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="R2" s="29" t="s">
         <v>377</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="34"/>
-    </row>
-    <row r="3" spans="1:20" ht="87" x14ac:dyDescent="0.35">
+      <c r="S2" s="30"/>
+      <c r="T2" s="34" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -1943,10 +1979,10 @@
         <v>4</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>5</v>
@@ -1975,17 +2011,17 @@
       <c r="P3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="35" t="s">
         <v>14</v>
       </c>
       <c r="R3" s="23" t="s">
-        <v>380</v>
+        <v>252</v>
       </c>
       <c r="S3" s="23" t="s">
-        <v>379</v>
+        <v>253</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>378</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
@@ -2002,11 +2038,11 @@
         <v>29</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F4" s="19"/>
       <c r="G4" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>218</v>
@@ -2035,13 +2071,13 @@
       <c r="P4" s="14"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S4" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T4" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
@@ -2056,11 +2092,11 @@
         <v>29</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F5" s="19"/>
       <c r="G5" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>211</v>
@@ -2089,13 +2125,13 @@
       <c r="P5" s="14"/>
       <c r="Q5" s="15"/>
       <c r="R5" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S5" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T5" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
@@ -2110,11 +2146,11 @@
         <v>29</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F6" s="19"/>
       <c r="G6" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>211</v>
@@ -2143,13 +2179,13 @@
       <c r="P6" s="14"/>
       <c r="Q6" s="15"/>
       <c r="R6" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
@@ -2164,11 +2200,11 @@
         <v>29</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>211</v>
@@ -2197,13 +2233,13 @@
       <c r="P7" s="14"/>
       <c r="Q7" s="15"/>
       <c r="R7" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T7" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
@@ -2220,23 +2256,23 @@
         <v>29</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F8" s="19"/>
       <c r="G8" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="I8" s="27" t="s">
-        <v>376</v>
+        <v>381</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>382</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="K8" s="27" t="s">
-        <v>373</v>
+        <v>380</v>
+      </c>
+      <c r="K8" s="33" t="s">
+        <v>379</v>
       </c>
       <c r="L8" s="11" t="s">
         <v>159</v>
@@ -2276,11 +2312,11 @@
         <v>29</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F9" s="19"/>
       <c r="G9" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>163</v>
@@ -2311,13 +2347,13 @@
       </c>
       <c r="Q9" s="15"/>
       <c r="R9" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S9" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T9" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
@@ -2334,11 +2370,11 @@
         <v>29</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F10" s="19"/>
       <c r="G10" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>163</v>
@@ -2367,13 +2403,13 @@
       <c r="P10" s="14"/>
       <c r="Q10" s="15"/>
       <c r="R10" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S10" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T10" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
@@ -2390,11 +2426,11 @@
         <v>29</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F11" s="19"/>
       <c r="G11" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>245</v>
@@ -2431,7 +2467,7 @@
         <v>16.681899999999999</v>
       </c>
       <c r="T11" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
@@ -2448,11 +2484,11 @@
         <v>29</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F12" s="19"/>
       <c r="G12" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>245</v>
@@ -2487,7 +2523,7 @@
         <v>19.1465</v>
       </c>
       <c r="T12" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
@@ -2504,11 +2540,11 @@
         <v>29</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F13" s="19"/>
       <c r="G13" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>227</v>
@@ -2537,13 +2573,13 @@
       <c r="P13" s="14"/>
       <c r="Q13" s="15"/>
       <c r="R13" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S13" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T13" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -2558,13 +2594,13 @@
         <v>29</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>22</v>
@@ -2616,13 +2652,13 @@
         <v>29</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>22</v>
@@ -2674,13 +2710,13 @@
         <v>29</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>22</v>
@@ -2732,13 +2768,13 @@
         <v>29</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>22</v>
@@ -2790,13 +2826,13 @@
         <v>29</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>22</v>
@@ -2848,11 +2884,11 @@
         <v>29</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F19" s="19"/>
       <c r="G19" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>239</v>
@@ -2902,13 +2938,13 @@
         <v>29</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>26</v>
@@ -2960,11 +2996,11 @@
         <v>29</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F21" s="19"/>
       <c r="G21" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>193</v>
@@ -3012,13 +3048,13 @@
         <v>29</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>26</v>
@@ -3070,13 +3106,13 @@
         <v>29</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>26</v>
@@ -3128,13 +3164,13 @@
         <v>29</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>26</v>
@@ -3186,13 +3222,13 @@
         <v>29</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>26</v>
@@ -3244,13 +3280,13 @@
         <v>29</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>26</v>
@@ -3279,13 +3315,13 @@
       <c r="P26" s="14"/>
       <c r="Q26" s="15"/>
       <c r="R26" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S26" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T26" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.35">
@@ -3300,11 +3336,11 @@
         <v>29</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F27" s="19"/>
       <c r="G27" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>129</v>
@@ -3354,11 +3390,11 @@
         <v>29</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F28" s="19"/>
       <c r="G28" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>129</v>
@@ -3408,11 +3444,11 @@
         <v>29</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F29" s="19"/>
       <c r="G29" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>129</v>
@@ -3462,11 +3498,11 @@
         <v>29</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F30" s="19"/>
       <c r="G30" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>134</v>
@@ -3518,11 +3554,11 @@
         <v>29</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F31" s="19"/>
       <c r="G31" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>173</v>
@@ -3553,13 +3589,13 @@
       </c>
       <c r="Q31" s="15"/>
       <c r="R31" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S31" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T31" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.35">
@@ -3574,13 +3610,13 @@
         <v>29</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>26</v>
@@ -3632,13 +3668,13 @@
         <v>29</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>26</v>
@@ -3690,13 +3726,13 @@
         <v>29</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>26</v>
@@ -3748,13 +3784,13 @@
         <v>29</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>26</v>
@@ -3806,13 +3842,13 @@
         <v>29</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>26</v>
@@ -3864,13 +3900,13 @@
         <v>29</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>26</v>
@@ -3922,11 +3958,11 @@
         <v>29</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F38" s="19"/>
       <c r="G38" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>199</v>
@@ -3976,13 +4012,13 @@
         <v>29</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H39" s="12" t="s">
         <v>27</v>
@@ -4034,11 +4070,11 @@
         <v>29</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F40" s="19"/>
       <c r="G40" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>67</v>
@@ -4090,11 +4126,11 @@
         <v>29</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F41" s="19"/>
       <c r="G41" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>67</v>
@@ -4146,11 +4182,11 @@
         <v>29</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F42" s="19"/>
       <c r="G42" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>67</v>
@@ -4202,11 +4238,11 @@
         <v>29</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F43" s="19"/>
       <c r="G43" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>67</v>
@@ -4235,13 +4271,13 @@
       <c r="P43" s="14"/>
       <c r="Q43" s="15"/>
       <c r="R43" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S43" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T43" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.35">
@@ -4256,11 +4292,11 @@
         <v>29</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F44" s="19"/>
       <c r="G44" s="11" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>137</v>
@@ -4310,11 +4346,11 @@
         <v>29</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F45" s="19"/>
       <c r="G45" s="11" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H45" s="12" t="s">
         <v>140</v>
@@ -4364,11 +4400,11 @@
         <v>29</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F46" s="19"/>
       <c r="G46" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>144</v>
@@ -4418,14 +4454,14 @@
         <v>29</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F47" s="19"/>
       <c r="G47" s="11" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="I47" s="21"/>
       <c r="J47" s="18" t="s">
@@ -4458,7 +4494,7 @@
         <v>78.078299999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="12" t="s">
         <v>209</v>
       </c>
@@ -4470,11 +4506,11 @@
         <v>70</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F48" s="19"/>
       <c r="G48" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H48" s="12" t="s">
         <v>211</v>
@@ -4503,13 +4539,13 @@
       <c r="P48" s="14"/>
       <c r="Q48" s="15"/>
       <c r="R48" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S48" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T48" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.35">
@@ -4524,11 +4560,11 @@
         <v>70</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F49" s="19"/>
       <c r="G49" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H49" s="12" t="s">
         <v>146</v>
@@ -4557,13 +4593,13 @@
       <c r="P49" s="14"/>
       <c r="Q49" s="15"/>
       <c r="R49" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S49" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T49" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.35">
@@ -4578,13 +4614,13 @@
         <v>70</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H50" s="12" t="s">
         <v>71</v>
@@ -4634,13 +4670,13 @@
         <v>70</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H51" s="12" t="s">
         <v>76</v>
@@ -4690,13 +4726,13 @@
         <v>70</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H52" s="12" t="s">
         <v>80</v>
@@ -4748,11 +4784,11 @@
         <v>70</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F53" s="19"/>
       <c r="G53" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H53" s="12" t="s">
         <v>178</v>
@@ -4787,7 +4823,7 @@
         <v>24.039200000000001</v>
       </c>
       <c r="T53" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.35">
@@ -4802,13 +4838,13 @@
         <v>70</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H54" s="12" t="s">
         <v>16</v>
@@ -4860,13 +4896,13 @@
         <v>70</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H55" s="12" t="s">
         <v>16</v>
@@ -4918,13 +4954,13 @@
         <v>70</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H56" s="12" t="s">
         <v>16</v>
@@ -4974,13 +5010,13 @@
         <v>70</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H57" s="12" t="s">
         <v>22</v>
@@ -5032,13 +5068,13 @@
         <v>70</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H58" s="12" t="s">
         <v>22</v>
@@ -5090,13 +5126,13 @@
         <v>70</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H59" s="12" t="s">
         <v>22</v>
@@ -5146,13 +5182,13 @@
         <v>70</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H60" s="12" t="s">
         <v>24</v>
@@ -5204,13 +5240,13 @@
         <v>70</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H61" s="12" t="s">
         <v>24</v>
@@ -5262,13 +5298,13 @@
         <v>70</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H62" s="12" t="s">
         <v>24</v>
@@ -5318,11 +5354,11 @@
         <v>70</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F63" s="19"/>
       <c r="G63" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H63" s="12" t="s">
         <v>149</v>
@@ -5374,13 +5410,13 @@
         <v>70</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H64" s="12" t="s">
         <v>26</v>
@@ -5432,13 +5468,13 @@
         <v>70</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H65" s="12" t="s">
         <v>90</v>
@@ -5488,13 +5524,13 @@
         <v>70</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H66" s="12" t="s">
         <v>90</v>
@@ -5546,13 +5582,13 @@
         <v>70</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H67" s="12" t="s">
         <v>90</v>
@@ -5604,13 +5640,13 @@
         <v>70</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H68" s="12" t="s">
         <v>90</v>
@@ -5660,13 +5696,13 @@
         <v>70</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H69" s="12" t="s">
         <v>93</v>
@@ -5716,13 +5752,13 @@
         <v>70</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H70" s="12" t="s">
         <v>93</v>
@@ -5760,7 +5796,7 @@
         <v>8081.16</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" s="12" t="s">
         <v>192</v>
       </c>
@@ -5774,11 +5810,11 @@
         <v>70</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F71" s="19"/>
       <c r="G71" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H71" s="12" t="s">
         <v>205</v>
@@ -5832,11 +5868,11 @@
         <v>70</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F72" s="19"/>
       <c r="G72" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>151</v>
@@ -5848,7 +5884,7 @@
         <v>155</v>
       </c>
       <c r="K72" s="16" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L72" s="17" t="s">
         <v>122</v>
@@ -5890,11 +5926,11 @@
         <v>70</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F73" s="19"/>
       <c r="G73" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H73" s="12" t="s">
         <v>151</v>
@@ -5906,7 +5942,7 @@
         <v>155</v>
       </c>
       <c r="K73" s="16" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L73" s="17" t="s">
         <v>122</v>
@@ -5948,11 +5984,11 @@
         <v>70</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F74" s="19"/>
       <c r="G74" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H74" s="12" t="s">
         <v>151</v>
@@ -5964,7 +6000,7 @@
         <v>155</v>
       </c>
       <c r="K74" s="16" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L74" s="17" t="s">
         <v>122</v>
@@ -6006,11 +6042,11 @@
         <v>70</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F75" s="19"/>
       <c r="G75" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H75" s="12" t="s">
         <v>151</v>
@@ -6022,7 +6058,7 @@
         <v>155</v>
       </c>
       <c r="K75" s="16" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L75" s="17" t="s">
         <v>122</v>
@@ -6064,11 +6100,11 @@
         <v>70</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F76" s="19"/>
       <c r="G76" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H76" s="12" t="s">
         <v>151</v>
@@ -6080,7 +6116,7 @@
         <v>155</v>
       </c>
       <c r="K76" s="16" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L76" s="17" t="s">
         <v>122</v>
@@ -6118,13 +6154,13 @@
         <v>70</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H77" s="12" t="s">
         <v>94</v>
@@ -6176,13 +6212,13 @@
         <v>70</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H78" s="12" t="s">
         <v>94</v>
@@ -6234,13 +6270,13 @@
         <v>70</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H79" s="12" t="s">
         <v>26</v>
@@ -6290,13 +6326,13 @@
         <v>70</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H80" s="12" t="s">
         <v>97</v>
@@ -6348,13 +6384,13 @@
         <v>70</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F81" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H81" s="12" t="s">
         <v>97</v>
@@ -6406,13 +6442,13 @@
         <v>70</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F82" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H82" s="12" t="s">
         <v>26</v>
@@ -6462,13 +6498,13 @@
         <v>70</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F83" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H83" s="12" t="s">
         <v>26</v>
@@ -6520,13 +6556,13 @@
         <v>70</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F84" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H84" s="12" t="s">
         <v>26</v>
@@ -6578,13 +6614,13 @@
         <v>70</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F85" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H85" s="12" t="s">
         <v>26</v>
@@ -6634,13 +6670,13 @@
         <v>70</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F86" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H86" s="12" t="s">
         <v>100</v>
@@ -6690,13 +6726,13 @@
         <v>70</v>
       </c>
       <c r="E87" s="19" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F87" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H87" s="12" t="s">
         <v>100</v>
@@ -6746,13 +6782,13 @@
         <v>70</v>
       </c>
       <c r="E88" s="19" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F88" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H88" s="12" t="s">
         <v>100</v>
@@ -6802,11 +6838,11 @@
         <v>70</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F89" s="19"/>
       <c r="G89" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H89" s="12" t="s">
         <v>156</v>
@@ -6856,11 +6892,11 @@
         <v>70</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F90" s="19"/>
       <c r="G90" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H90" s="12" t="s">
         <v>157</v>
@@ -6910,11 +6946,11 @@
         <v>70</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F91" s="19"/>
       <c r="G91" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H91" s="12" t="s">
         <v>186</v>
@@ -6949,7 +6985,7 @@
         <v>123.68300000000001</v>
       </c>
       <c r="T91" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.35">
@@ -6964,13 +7000,13 @@
         <v>70</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F92" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H92" s="12" t="s">
         <v>102</v>
@@ -7022,13 +7058,13 @@
         <v>70</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F93" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H93" s="12" t="s">
         <v>102</v>
@@ -7080,13 +7116,13 @@
         <v>70</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F94" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H94" s="12" t="s">
         <v>102</v>
@@ -7136,13 +7172,13 @@
         <v>70</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F95" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H95" s="12" t="s">
         <v>104</v>
@@ -7194,13 +7230,13 @@
         <v>70</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F96" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H96" s="12" t="s">
         <v>104</v>
@@ -7250,13 +7286,13 @@
         <v>70</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F97" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G97" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H97" s="12" t="s">
         <v>104</v>
@@ -7306,13 +7342,13 @@
         <v>70</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F98" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H98" s="12" t="s">
         <v>107</v>
@@ -7341,13 +7377,13 @@
       <c r="P98" s="14"/>
       <c r="Q98" s="15"/>
       <c r="R98" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S98" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T98" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.35">
@@ -7362,11 +7398,11 @@
         <v>70</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F99" s="19"/>
       <c r="G99" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H99" s="12" t="s">
         <v>123</v>
@@ -7416,11 +7452,11 @@
         <v>70</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F100" s="19"/>
       <c r="G100" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H100" s="12" t="s">
         <v>158</v>
@@ -7470,11 +7506,11 @@
         <v>70</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F101" s="19"/>
       <c r="G101" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H101" s="12" t="s">
         <v>158</v>
@@ -7524,13 +7560,13 @@
         <v>110</v>
       </c>
       <c r="E102" s="19" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F102" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H102" s="12" t="s">
         <v>111</v>
@@ -7559,13 +7595,13 @@
       <c r="P102" s="14"/>
       <c r="Q102" s="15"/>
       <c r="R102" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S102" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T102" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.35">
@@ -7580,13 +7616,13 @@
         <v>110</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F103" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H103" s="12" t="s">
         <v>115</v>
@@ -7634,13 +7670,13 @@
         <v>110</v>
       </c>
       <c r="E104" s="19" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F104" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G104" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H104" s="12" t="s">
         <v>22</v>
@@ -7690,13 +7726,13 @@
         <v>110</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F105" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H105" s="12" t="s">
         <v>90</v>
@@ -7746,13 +7782,13 @@
         <v>110</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F106" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G106" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H106" s="12" t="s">
         <v>117</v>
@@ -7781,13 +7817,13 @@
       <c r="P106" s="14"/>
       <c r="Q106" s="15"/>
       <c r="R106" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="S106" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="T106" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.35">
@@ -7802,13 +7838,13 @@
         <v>110</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F107" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G107" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H107" s="12" t="s">
         <v>26</v>
@@ -7858,11 +7894,11 @@
         <v>110</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F108" s="19"/>
       <c r="G108" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H108" s="12" t="s">
         <v>123</v>
@@ -7908,36 +7944,36 @@
         <v>153</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D109" s="12" t="s">
         <v>110</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F109" s="12"/>
       <c r="G109" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="I109" s="12"/>
       <c r="J109" s="12" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K109" s="16" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="L109" s="17" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M109" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N109" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O109" s="17">
         <v>24.6</v>
@@ -8492,21 +8528,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AAFFF3D42354FC46AAF9DDD3E79C50EB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2dc978867c734327b61f3800eb63d242">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="e1d46fbb-7d1a-4672-bfd6-63f33723acfe" xmlns:ns4="5abdcbab-ff3d-4b55-bc16-63963a6146d3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c122bff22086de4b34442ce3fa7ec584" ns3:_="" ns4:_="">
     <xsd:import namespace="e1d46fbb-7d1a-4672-bfd6-63f33723acfe"/>
@@ -8735,32 +8756,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7132B4B-6BDC-47A9-AF0C-0341A70E6725}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="e1d46fbb-7d1a-4672-bfd6-63f33723acfe"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5abdcbab-ff3d-4b55-bc16-63963a6146d3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{454B4A55-1C62-49DF-B7EA-FD56AEB4B42C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58A6EA98-5C4B-47AC-A15E-1B7C0018A8AA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8777,4 +8788,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{454B4A55-1C62-49DF-B7EA-FD56AEB4B42C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7132B4B-6BDC-47A9-AF0C-0341A70E6725}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="e1d46fbb-7d1a-4672-bfd6-63f33723acfe"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5abdcbab-ff3d-4b55-bc16-63963a6146d3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>